--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62645.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62645.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>1G31103</t>
+          <t>1ë</t>
         </is>
       </c>
     </row>
@@ -463,11 +463,7 @@
           <t>Code</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>81-01-61</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -516,7 +512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -545,7 +541,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Klple juzllelylj</t>
+          <t>Bgpndel</t>
         </is>
       </c>
     </row>
@@ -557,7 +553,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LSUALULELL</t>
+          <t>SLDNY</t>
         </is>
       </c>
     </row>
@@ -579,7 +575,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G09D</t>
+          <t>G03D</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62645.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62645.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>51-01-61</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,11 @@
           <t>Code</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>51-01-G1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -512,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -575,7 +579,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G03D</t>
+          <t>G09C</t>
         </is>
       </c>
     </row>
@@ -596,7 +600,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62645.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62645.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bgpndel</t>
+          <t>Raphael</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SLDNY</t>
+          <t>SIANA</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>1001</v>
+        <v>42001</v>
       </c>
     </row>
     <row r="5">
@@ -721,10 +721,10 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>36</v>
+        <v>316</v>
       </c>
       <c r="K7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62645.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62645.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Raphael</t>
+          <t>RAPHAEL</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>316</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
         <v>12</v>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62645.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62645.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -703,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>42001</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +724,7 @@
         <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
